--- a/forms/trg/Formulir_TRG_pednrg.xlsx
+++ b/forms/trg/Formulir_TRG_pednrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B32)</f>
+        <f>COUNTA(Anggota!B5:B33)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F32)</f>
+        <f>COUNTA(Anggota!F5:F33)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Nur Fadilah, S.Kep., Ns., MN.</t>
+          <t>Prof. Dr. Kadek Ayu Erika, S.Kep., Ns., M.Kes.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Family and Child Health Nursing</t>
+          <t>Child Growth and Development</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,13 +937,13 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-5384-1589</t>
+          <t>0000-0001-6875-5264</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57205259699</t>
+          <t>57191058011</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Nurlaila Fitriani, S.Kep., Ns., M.Kep., Sp.Kep.J</t>
+          <t>Nur Fadilah, S.Kep., Ns., MN.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Mental Health in Adolescent</t>
+          <t>Family and Child Health Nursing</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,13 +982,13 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3844-0346</t>
+          <t>0000-0002-5384-1589</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57205117337</t>
+          <t>57205259699</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. dr. Martira Maddeppungeng, Sp.A (K)</t>
+          <t>Nurlaila Fitriani, S.Kep., Ns., M.Kep., Sp.Kep.J</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Child Growth and Development</t>
+          <t>Mental Health in Adolescent</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1027,15 +1027,15 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6109-6024</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/subjects/detail/112232</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="n"/>
+          <t>0000-0003-3844-0346</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57205117337</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Tuti Seniwati, S.Kep., Ns., M.Kes.</t>
+          <t>Dr. dr. Martira Maddeppungeng, Sp.A (K)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Pediatric Critical Care</t>
+          <t>Child Growth and Development</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1072,15 +1072,15 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7270-0493</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>57215875237</t>
-        </is>
-      </c>
+          <t>0000-0001-6109-6024</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/subjects/detail/112232</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1093,22 +1093,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Misita Anwar</t>
+          <t>Dr. Tuti Seniwati, S.Kep., Ns., M.Kes.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Monash University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Information System</t>
+          <t>Pediatric Critical Care</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1117,15 +1117,15 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3979-1746</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/scopusanalysis/6127778</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="n"/>
+          <t>0000-0001-7270-0493</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>57215875237</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1138,30 +1138,38 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Mary Nathalie M. Cata-al</t>
+          <t>Dr. Misita Anwar</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>College of Nursing – Silliman University</t>
+          <t>Monash University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Psychiatric Mental Health Nursing</t>
+          <t>Information System</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-3979-1746</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/scopusanalysis/6127778</t>
+        </is>
+      </c>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
@@ -1175,22 +1183,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Yoko AIHARA</t>
+          <t>Mary Nathalie M. Cata-al</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Health Sciences – Okayama University</t>
+          <t>College of Nursing – Silliman University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Community Health and Nursing</t>
+          <t>Psychiatric Mental Health Nursing</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1212,39 +1220,31 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Mgr. Eva Hlaváčková, Ph.D.</t>
+          <t>Prof. Yoko AIHARA</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Health Studies – University of Pardubice</t>
+          <t>Faculty of Health Sciences – Okayama University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Department of Clinical Subspecialities</t>
+          <t>Community Health and Nursing</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-0792-4567</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>36537053800</t>
-        </is>
-      </c>
+      <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Arbianingsih, S.Kep., Ns., M.Kes.</t>
+          <t>Mgr. Eva Hlaváčková, Ph.D.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Alauddin State Islamic University Makassar</t>
+          <t>Faculty of Health Studies – University of Pardubice</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Technology Platform Development</t>
+          <t>Department of Clinical Subspecialities</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1281,13 +1281,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6658-8490</t>
+          <t>0000-0003-0792-4567</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57201489106</t>
+          <t>36537053800</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1302,31 +1302,39 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Indah Reski Amallia, S.Kep., Ns., M.Kep., Sp.Kep.A</t>
+          <t>Dr. Arbianingsih, S.Kep., Ns., M.Kes.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University Hospital, Makassar</t>
+          <t>Alauddin State Islamic University Makassar</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Child Growth and Development</t>
+          <t>Technology Platform Development</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-6658-8490</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>57201489106</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1339,39 +1347,31 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Nuzul Qur’aniati, S.Kep., Ns., M.Ng., Ph.D</t>
+          <t>Indah Reski Amallia, S.Kep., Ns., M.Kep., Sp.Kep.A</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Airlangga University</t>
+          <t>Hasanuddin University Hospital, Makassar</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Family and Child Health Nursing</t>
+          <t>Child Growth and Development</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-3939-6482</t>
-        </is>
-      </c>
+      <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>57417735300</t>
-        </is>
-      </c>
+      <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1384,31 +1384,39 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Sara Regina dos Reis Pires, S.Kep., Ns.</t>
+          <t>Nuzul Qur’aniati, S.Kep., Ns., M.Ng., Ph.D</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Airlangga University</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Child Health Nursing</t>
+          <t>Family and Child Health Nursing</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-3939-6482</t>
+        </is>
+      </c>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>57417735300</t>
+        </is>
+      </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1421,12 +1429,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Muti Sahida. UM, S.Kep., Ns.</t>
+          <t>Sara Regina dos Reis Pires, S.Kep., Ns.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1436,18 +1444,14 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Nursing Science</t>
+          <t>Child Health Nursing</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>0009-0003-3076-831X</t>
-        </is>
-      </c>
+      <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
@@ -1462,12 +1466,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Yulita Palembangan, S.Kep., Ns.</t>
+          <t>Muti Sahida. UM, S.Kep., Ns.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1477,7 +1481,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Pediatric Nursing</t>
+          <t>Nursing Science</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1486,7 +1490,7 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0009-0007-2612-8319</t>
+          <t>0009-0003-3076-831X</t>
         </is>
       </c>
       <c r="K18" s="12" t="n"/>
@@ -1503,12 +1507,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Cristian Somalinggi, S.Kep., Ns.</t>
+          <t>Yulita Palembangan, S.Kep., Ns.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1527,7 +1531,7 @@
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-1044-1010</t>
+          <t>0009-0007-2612-8319</t>
         </is>
       </c>
       <c r="K19" s="12" t="n"/>
@@ -1544,22 +1548,22 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Ninda Regita Cahyani, S.Kep., Ns.</t>
+          <t>Cristian Somalinggi, S.Kep., Ns.</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
           <t>Pediatric Nursing</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>PEDNRG Team</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1568,7 +1572,7 @@
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-9955-8140</t>
+          <t>0009-0003-1044-1010</t>
         </is>
       </c>
       <c r="K20" s="12" t="n"/>
@@ -1583,18 +1587,42 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Ninda Regita Cahyani, S.Kep., Ns.</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Pediatric Nursing</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>PEDNRG Team</t>
+        </is>
+      </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0009-0000-9955-8140</t>
+        </is>
+      </c>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1783,15 +1811,32 @@
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="12" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
